--- a/artfynd/A 19430-2026 artfynd.xlsx
+++ b/artfynd/A 19430-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136413726</v>
       </c>
       <c r="B2" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2026 artfynd.xlsx
+++ b/artfynd/A 19430-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136413726</v>
       </c>
       <c r="B2" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136413978</v>
       </c>
       <c r="B3" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136412135</v>
       </c>
       <c r="B4" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136413566</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136413647</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136413680</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136413689</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136414352</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136414731</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>136414333</v>
       </c>
       <c r="B11" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136411441</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>136414722</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>136414742</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2026 artfynd.xlsx
+++ b/artfynd/A 19430-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136413726</v>
       </c>
       <c r="B2" t="n">
-        <v>89472</v>
+        <v>89474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2026 artfynd.xlsx
+++ b/artfynd/A 19430-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136413726</v>
       </c>
       <c r="B2" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136413978</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136412135</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136413566</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136413647</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136413680</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136413689</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136414352</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136414731</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2026 artfynd.xlsx
+++ b/artfynd/A 19430-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136413726</v>
       </c>
       <c r="B2" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136413978</v>
       </c>
       <c r="B3" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136412135</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136413566</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136413647</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136413680</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136413689</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136414352</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136414731</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2026 artfynd.xlsx
+++ b/artfynd/A 19430-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136413726</v>
       </c>
       <c r="B2" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136413978</v>
       </c>
       <c r="B3" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136412135</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136413566</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136413647</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136413680</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136413689</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136414352</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136414731</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
